--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484878_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484878_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.653499999999999</v>
+        <v>7.8741</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8604</v>
+        <v>5.4778</v>
       </c>
       <c r="F2" t="n">
-        <v>2.793</v>
+        <v>2.3962</v>
       </c>
       <c r="G2" t="n">
         <v>2.1479</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1321</v>
+        <v>1.3527</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0721</v>
+        <v>0.6895</v>
       </c>
       <c r="U2" t="n">
-        <v>1.06</v>
+        <v>0.6632</v>
       </c>
       <c r="V2" t="n">
         <v>3.0526</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.133</v>
+        <v>7.7532</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6363</v>
+        <v>4.7539</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4967</v>
+        <v>2.9993</v>
       </c>
       <c r="G3" t="n">
         <v>8.135199999999999</v>
@@ -688,13 +688,13 @@
         <v>2.8305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0176</v>
+        <v>0.6026</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2409</v>
+        <v>0.3585</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2586</v>
+        <v>0.2441</v>
       </c>
       <c r="V3" t="n">
         <v>-2.8716</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.241</v>
+        <v>3.8991</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3317</v>
+        <v>2.2544</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9093</v>
+        <v>1.6448</v>
       </c>
       <c r="G4" t="n">
         <v>2.4933</v>
@@ -766,13 +766,13 @@
         <v>0.9435</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1663</v>
+        <v>0.8245</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5349</v>
+        <v>0.4576</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6314</v>
+        <v>0.3669</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3622</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0634</v>
+        <v>3.6623</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2113</v>
+        <v>1.1542</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8521</v>
+        <v>2.5081</v>
       </c>
       <c r="G5" t="n">
         <v>2.7874</v>
@@ -844,13 +844,13 @@
         <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5814</v>
+        <v>0.1804</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0058</v>
+        <v>-0.0514</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5756</v>
+        <v>0.2317</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0038</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. CARRIÓN GALINDO</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4848</v>
+        <v>2.8495</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4848</v>
+        <v>1.3387</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.5108</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4848</v>
+        <v>6.4176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6339</v>
+        <v>5.3717</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8509</v>
+        <v>1.0458</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4848</v>
+        <v>5.797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6339</v>
+        <v>5.7474</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8509</v>
+        <v>0.0496</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.3756</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.9962</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-5.4723</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-6.6045</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3382</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.0234</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.3616</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.566</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>L. CARRIÓN GALINDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4408</v>
+        <v>2.4848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4803</v>
+        <v>2.4848</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9605</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4176</v>
+        <v>2.4848</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3717</v>
+        <v>0.6339</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0458</v>
+        <v>1.8509</v>
       </c>
       <c r="J7" t="n">
-        <v>5.797</v>
+        <v>2.4848</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7474</v>
+        <v>0.6339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0496</v>
+        <v>1.8509</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6205000000000001</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3756</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9962</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.4723</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.6045</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8818</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8114</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.566</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8915999999999999</v>
+        <v>1.5622</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1609</v>
+        <v>2.4347</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2694</v>
+        <v>-0.8726</v>
       </c>
       <c r="G8" t="n">
         <v>2.1369</v>
@@ -1078,13 +1078,13 @@
         <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8306</v>
+        <v>-0.16</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4674</v>
+        <v>-0.1936</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3632</v>
+        <v>0.0336</v>
       </c>
       <c r="V8" t="n">
         <v>-2.4904</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>L. CARRION GALINDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7461</v>
+        <v>0.3083</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2517</v>
+        <v>-3.7011</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4945</v>
+        <v>4.0095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1393</v>
+        <v>-0.703</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1205</v>
+        <v>0.583</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2598</v>
+        <v>-1.2861</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0423</v>
+        <v>-2.4017</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0423</v>
+        <v>-0.6175</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.7842</v>
       </c>
       <c r="M9" t="n">
-        <v>0.097</v>
+        <v>1.6986</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1628</v>
+        <v>1.2005</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2598</v>
+        <v>0.4981</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3774</v>
+        <v>2.6418</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0176</v>
+        <v>-0.3248</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2939</v>
+        <v>-0.356</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2763</v>
+        <v>0.0312</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2452</v>
+        <v>-0.3622</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2452</v>
+        <v>-0.3622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. CARRION GALINDO</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.923</v>
+        <v>-0.5777</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4033</v>
+        <v>-0.0568</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4804</v>
+        <v>-0.5209</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.703</v>
+        <v>0.1393</v>
       </c>
       <c r="H10" t="n">
-        <v>0.583</v>
+        <v>-0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2861</v>
+        <v>0.2598</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4017</v>
+        <v>0.0423</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6175</v>
+        <v>0.0423</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7842</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6986</v>
+        <v>0.097</v>
       </c>
       <c r="N10" t="n">
-        <v>1.2005</v>
+        <v>-0.1628</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4981</v>
+        <v>0.2598</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6418</v>
+        <v>0.3774</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.556</v>
+        <v>0.1508</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0582</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4979</v>
+        <v>0.2498</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3622</v>
+        <v>-1.2452</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3622</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6716</v>
+        <v>-1.347</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2235</v>
+        <v>-1.8724</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5518</v>
+        <v>0.5254</v>
       </c>
       <c r="G11" t="n">
         <v>0.3197</v>
@@ -1312,13 +1312,13 @@
         <v>0.9435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4444</v>
+        <v>-0.1197</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5291</v>
+        <v>-0.178</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0847</v>
+        <v>0.0582</v>
       </c>
       <c r="V11" t="n">
         <v>-1.547</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.904</v>
+        <v>-1.6297</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3014</v>
+        <v>-2.1065</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3974</v>
+        <v>0.4768</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8516</v>
@@ -1390,13 +1390,13 @@
         <v>0.1887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.241</v>
+        <v>0.0332</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1117</v>
+        <v>0.1911</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>25.6634</v>
+        <v>26.8391</v>
       </c>
       <c r="E13" t="n">
-        <v>10.9858</v>
+        <v>12.1617</v>
       </c>
       <c r="F13" t="n">
-        <v>14.6773</v>
+        <v>14.6774</v>
       </c>
       <c r="G13" t="n">
         <v>24.5075</v>
@@ -1438,7 +1438,7 @@
         <v>23.6422</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8651999999999999</v>
+        <v>0.8652000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>16.8873</v>
@@ -1447,10 +1447,10 @@
         <v>20.2457</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.358299999999999</v>
+        <v>-3.3583</v>
       </c>
       <c r="M13" t="n">
-        <v>7.6199</v>
+        <v>7.619900000000001</v>
       </c>
       <c r="N13" t="n">
         <v>3.3966</v>
@@ -1468,16 +1468,16 @@
         <v>16.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7021</v>
+        <v>2.8779</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7294000000000002</v>
+        <v>0.4462000000000003</v>
       </c>
       <c r="U13" t="n">
         <v>2.4314</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.2638</v>
+        <v>-5.263800000000001</v>
       </c>
       <c r="W13" t="n">
         <v>6.15</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1046</v>
+        <v>-0.8576</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5754</v>
+        <v>0.796</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.68</v>
+        <v>-1.6535</v>
       </c>
       <c r="G14" t="n">
         <v>-2.3291</v>
@@ -1546,13 +1546,13 @@
         <v>2.2644</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8588</v>
+        <v>0.1058</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7294</v>
+        <v>-0.0501</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1294</v>
+        <v>0.1559</v>
       </c>
       <c r="V14" t="n">
         <v>2.8753</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.2495</v>
+        <v>-5.1674</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8738</v>
+        <v>-3.6111</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3757</v>
+        <v>-1.5562</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.7787</v>
+        <v>-4.7004</v>
       </c>
       <c r="H16" t="n">
-        <v>-6.1442</v>
+        <v>-2.7672</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6345</v>
+        <v>-1.9331</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.4013</v>
+        <v>-2.3481</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0951</v>
+        <v>-0.5228</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3062</v>
+        <v>-1.8253</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3775</v>
+        <v>-2.3523</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.0491</v>
+        <v>-2.2445</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6717</v>
+        <v>-0.1078</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2644</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5484</v>
+        <v>-1.3991</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0378</v>
+        <v>-1.244</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5862</v>
+        <v>-0.1551</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4904</v>
+        <v>0.366</v>
       </c>
       <c r="W16" t="n">
-        <v>4.3392</v>
+        <v>0.9244</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8488</v>
+        <v>-0.5584</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. DURAN OLMOS</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.6605</v>
+        <v>-5.2133</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.9744</v>
+        <v>-2.6489</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6862</v>
+        <v>-2.5644</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.6445</v>
+        <v>-2.6768</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.4218</v>
+        <v>-3.2767</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2227</v>
+        <v>0.5999</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.1823</v>
+        <v>0.2123</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0066</v>
+        <v>0.1541</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1757</v>
+        <v>0.0582</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4622</v>
+        <v>-2.8891</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.4152</v>
+        <v>-3.4309</v>
       </c>
       <c r="O17" t="n">
-        <v>0.953</v>
+        <v>0.5417</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9435</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9435</v>
+        <v>-4.7175</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3821</v>
+        <v>-0.3172</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4522</v>
+        <v>-0.2943</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.0229</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5774</v>
+        <v>0.9886</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036</v>
+        <v>2.1506</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.181</v>
+        <v>-1.1621</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>I. DURAN OLMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.9539</v>
+        <v>-5.4308</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.0009</v>
+        <v>-3.8769</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9531</v>
+        <v>-1.5539</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.7004</v>
+        <v>-5.6445</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7672</v>
+        <v>-5.4218</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9331</v>
+        <v>-0.2227</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3481</v>
+        <v>-3.1823</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5228</v>
+        <v>-2.0066</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8253</v>
+        <v>-1.1757</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3523</v>
+        <v>-2.4622</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2445</v>
+        <v>-3.4152</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1078</v>
+        <v>0.953</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1857</v>
+        <v>-0.1524</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6337</v>
+        <v>-0.3547</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.2023</v>
       </c>
       <c r="V18" t="n">
-        <v>0.366</v>
+        <v>-0.5774</v>
       </c>
       <c r="W18" t="n">
-        <v>0.9244</v>
+        <v>0.6036</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5584</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.1683</v>
+        <v>-5.4677</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2335</v>
+        <v>-3.1661</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9348</v>
+        <v>-2.3016</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6768</v>
+        <v>-6.7787</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.2767</v>
+        <v>-6.1442</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5999</v>
+        <v>-0.6345</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2123</v>
+        <v>-3.4013</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1541</v>
+        <v>-2.0951</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0582</v>
+        <v>-1.3062</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8891</v>
+        <v>-3.3775</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.4309</v>
+        <v>-4.0491</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5417</v>
+        <v>0.6717</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.2079</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.7175</v>
+        <v>-3.774</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5096</v>
+        <v>2.2644</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2721</v>
+        <v>0.3302</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8789</v>
+        <v>-0.3301</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3932</v>
+        <v>0.6603</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9886</v>
+        <v>2.4904</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1506</v>
+        <v>4.3392</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1621</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="20">
@@ -1972,10 +1972,10 @@
         <v>-25.6632</v>
       </c>
       <c r="E20" t="n">
-        <v>-14.6774</v>
+        <v>-14.6772</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.986</v>
+        <v>-10.9858</v>
       </c>
       <c r="G20" t="n">
         <v>-24.5074</v>
@@ -2005,7 +2005,7 @@
         <v>3.3582</v>
       </c>
       <c r="P20" t="n">
-        <v>-4.7175</v>
+        <v>-4.717499999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>-16.0395</v>
